--- a/ktds/AI/AI_Agentic AI 커리큘럼_KTDS.xlsx
+++ b/ktds/AI/AI_Agentic AI 커리큘럼_KTDS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dreamondal/Documents/제안/KTDS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hiond\Documents\unicorn-campus\ktds\AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31492D1-2337-FB4C-A49A-80D3B933CCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0FE5DB-AE71-4D38-99F3-D0B9F86D0108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI 교육 커리큘럼" sheetId="2" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'AI 교육 커리큘럼'!$4:$4</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>교육 목표</t>
   </si>
@@ -151,10 +164,6 @@
     <t xml:space="preserve">[실습]
 • Function Calling 실습: Travel Planner
 - 날씨, 관광지, 음식점을 검색하여 여행 장소 부근의 오늘의 여행 루트 추천 </t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.5H</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -203,9 +212,6 @@
   <si>
     <t>[실습]
 • MCP 서버 구현 및 Claude 연동 실습</t>
-  </si>
-  <si>
-    <t>2H</t>
   </si>
   <si>
     <t>LangGraph &amp; MAS
@@ -262,31 +268,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>4.5H</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Claude 플러그인
-동작 원리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">■ Claude Code 플러그인 구성요소 이해
- - Commands, Skills, Agents의 역할과 관계
- - 선언적 방식의 플러그인 사용 방법 이해
-</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[실습]
-- blog poster 개발 
-  - 주제 키워드 입력 
-  - 웹검색, 기술문서 조사, 트렌드 분석 
-  - SEO 최적화 , AI 이미지 생성 
-  - 최종 Word 문서 생성 
-</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>Wrap-up</t>
   </si>
   <si>
@@ -300,13 +281,34 @@
   </si>
   <si>
     <t>0.5H</t>
+  </si>
+  <si>
+    <t>멀티모달 기반 기능</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 문서요약, PDF 변환, STT, TTS, VLM에서 클라우드/로컬 LLM 모델 활용</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[실습]
+멀티모달 예제 실습</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2H</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.5H</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,7 +400,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -469,12 +471,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -484,49 +510,61 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -835,203 +873,203 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8" style="5" customWidth="1"/>
-    <col min="2" max="2" width="22" style="5" customWidth="1"/>
-    <col min="3" max="3" width="58" style="5" customWidth="1"/>
-    <col min="4" max="4" width="45.1640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="7" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="5"/>
+    <col min="1" max="1" width="8" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22" style="3" customWidth="1"/>
+    <col min="3" max="3" width="58" style="3" customWidth="1"/>
+    <col min="4" max="4" width="45.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="7" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
+    <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="3"/>
+      <c r="C1" s="16"/>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="35" customHeight="1">
+    <row r="2" spans="1:5" ht="35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="16"/>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20" customHeight="1">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="22" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="150">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:5" ht="145" x14ac:dyDescent="0.45">
+      <c r="A5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="120">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10" t="s">
+    <row r="6" spans="1:5" ht="116" x14ac:dyDescent="0.45">
+      <c r="A6" s="18"/>
+      <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="181" customHeight="1">
-      <c r="A7" s="15"/>
-      <c r="B7" s="10" t="s">
+    <row r="7" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="19"/>
+      <c r="B7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="206" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="20"/>
+      <c r="B8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E8" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="206" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="206" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17" t="s">
+      <c r="C9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="D9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="152.5" customHeight="1">
-      <c r="A9" s="9" t="s">
+      <c r="E9" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="152.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="23"/>
+      <c r="B10" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="C10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="E10" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="409.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="23"/>
+      <c r="B11" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="C11" s="8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="409.5" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="20" t="s">
+      <c r="D11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="E11" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="24"/>
+      <c r="B12" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="C12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="D12" s="8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="123.5" customHeight="1">
-      <c r="A11" s="16"/>
-      <c r="B11" s="20" t="s">
+      <c r="E12" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="42" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A9:A12"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A5:A8"/>
-    <mergeCell ref="A9:A12"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
